--- a/artfynd/A 16982-2023 artfynd.xlsx
+++ b/artfynd/A 16982-2023 artfynd.xlsx
@@ -1417,10 +1417,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125893499</v>
+        <v>125893478</v>
       </c>
       <c r="B8" t="n">
-        <v>58325</v>
+        <v>57524</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1428,16 +1428,16 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103044</v>
+        <v>100096</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Fiskgjuse</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Pandion haliaetus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1663,10 +1663,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125893478</v>
+        <v>125893499</v>
       </c>
       <c r="B10" t="n">
-        <v>57524</v>
+        <v>58325</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1674,16 +1674,16 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100096</v>
+        <v>103044</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Fiskgjuse</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pandion haliaetus</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">

--- a/artfynd/A 16982-2023 artfynd.xlsx
+++ b/artfynd/A 16982-2023 artfynd.xlsx
@@ -801,7 +801,7 @@
         <v>125893495</v>
       </c>
       <c r="B3" t="n">
-        <v>58153</v>
+        <v>58154</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1170,7 +1170,7 @@
         <v>125893493</v>
       </c>
       <c r="B6" t="n">
-        <v>58083</v>
+        <v>58084</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1543,7 +1543,7 @@
         <v>125893492</v>
       </c>
       <c r="B9" t="n">
-        <v>58078</v>
+        <v>58079</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1666,7 +1666,7 @@
         <v>125893499</v>
       </c>
       <c r="B10" t="n">
-        <v>58325</v>
+        <v>58326</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 16982-2023 artfynd.xlsx
+++ b/artfynd/A 16982-2023 artfynd.xlsx
@@ -1417,44 +1417,44 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125893478</v>
+        <v>125893492</v>
       </c>
       <c r="B8" t="n">
-        <v>57524</v>
+        <v>58079</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100096</v>
+        <v>103001</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Fiskgjuse</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pandion haliaetus</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1766</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>förbiflygande</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
@@ -1540,44 +1540,44 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125893492</v>
+        <v>125893499</v>
       </c>
       <c r="B9" t="n">
-        <v>58079</v>
+        <v>58326</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103001</v>
+        <v>103044</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>förbiflygande</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
@@ -1663,10 +1663,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125893499</v>
+        <v>125893478</v>
       </c>
       <c r="B10" t="n">
-        <v>58326</v>
+        <v>57524</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1674,16 +1674,16 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103044</v>
+        <v>100096</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Fiskgjuse</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Pandion haliaetus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">

--- a/artfynd/A 16982-2023 artfynd.xlsx
+++ b/artfynd/A 16982-2023 artfynd.xlsx
@@ -1417,44 +1417,44 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125893492</v>
+        <v>125893478</v>
       </c>
       <c r="B8" t="n">
-        <v>58079</v>
+        <v>57524</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103001</v>
+        <v>100096</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Fiskgjuse</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Pandion haliaetus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>förbiflygande</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
@@ -1663,44 +1663,44 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125893478</v>
+        <v>125893492</v>
       </c>
       <c r="B10" t="n">
-        <v>57524</v>
+        <v>58079</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100096</v>
+        <v>103001</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Fiskgjuse</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pandion haliaetus</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1766</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>förbiflygande</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>

--- a/artfynd/A 16982-2023 artfynd.xlsx
+++ b/artfynd/A 16982-2023 artfynd.xlsx
@@ -1540,44 +1540,44 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125893499</v>
+        <v>125893492</v>
       </c>
       <c r="B9" t="n">
-        <v>58326</v>
+        <v>58079</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103044</v>
+        <v>103001</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1766</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>förbiflygande</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
@@ -1663,44 +1663,44 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125893492</v>
+        <v>125893499</v>
       </c>
       <c r="B10" t="n">
-        <v>58079</v>
+        <v>58326</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103001</v>
+        <v>103044</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>förbiflygande</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>

--- a/artfynd/A 16982-2023 artfynd.xlsx
+++ b/artfynd/A 16982-2023 artfynd.xlsx
@@ -1417,44 +1417,44 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125893478</v>
+        <v>125893492</v>
       </c>
       <c r="B8" t="n">
-        <v>57524</v>
+        <v>58079</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100096</v>
+        <v>103001</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Fiskgjuse</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pandion haliaetus</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1766</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>förbiflygande</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
@@ -1540,44 +1540,44 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125893492</v>
+        <v>125893478</v>
       </c>
       <c r="B9" t="n">
-        <v>58079</v>
+        <v>57524</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103001</v>
+        <v>100096</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Fiskgjuse</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Pandion haliaetus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>förbiflygande</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>

--- a/artfynd/A 16982-2023 artfynd.xlsx
+++ b/artfynd/A 16982-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125893477</v>
       </c>
       <c r="B2" t="n">
-        <v>57257</v>
+        <v>57258</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -801,7 +801,7 @@
         <v>125893495</v>
       </c>
       <c r="B3" t="n">
-        <v>58154</v>
+        <v>58155</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -924,7 +924,7 @@
         <v>125893485</v>
       </c>
       <c r="B4" t="n">
-        <v>57601</v>
+        <v>57602</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1047,7 +1047,7 @@
         <v>125893474</v>
       </c>
       <c r="B5" t="n">
-        <v>56958</v>
+        <v>56959</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1170,7 +1170,7 @@
         <v>125893493</v>
       </c>
       <c r="B6" t="n">
-        <v>58084</v>
+        <v>58085</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1293,7 +1293,7 @@
         <v>125893484</v>
       </c>
       <c r="B7" t="n">
-        <v>57597</v>
+        <v>57598</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1417,44 +1417,44 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125893492</v>
+        <v>125893478</v>
       </c>
       <c r="B8" t="n">
-        <v>58079</v>
+        <v>57525</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103001</v>
+        <v>100096</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Fiskgjuse</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Pandion haliaetus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>förbiflygande</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
@@ -1540,44 +1540,44 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125893478</v>
+        <v>125893492</v>
       </c>
       <c r="B9" t="n">
-        <v>57524</v>
+        <v>58080</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100096</v>
+        <v>103001</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Fiskgjuse</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pandion haliaetus</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1766</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>förbiflygande</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
@@ -1666,7 +1666,7 @@
         <v>125893499</v>
       </c>
       <c r="B10" t="n">
-        <v>58326</v>
+        <v>58327</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1789,7 +1789,7 @@
         <v>125893472</v>
       </c>
       <c r="B11" t="n">
-        <v>57473</v>
+        <v>57474</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 16982-2023 artfynd.xlsx
+++ b/artfynd/A 16982-2023 artfynd.xlsx
@@ -1417,10 +1417,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125893478</v>
+        <v>125893499</v>
       </c>
       <c r="B8" t="n">
-        <v>57525</v>
+        <v>58327</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1428,16 +1428,16 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100096</v>
+        <v>103044</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Fiskgjuse</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pandion haliaetus</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1663,10 +1663,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125893499</v>
+        <v>125893478</v>
       </c>
       <c r="B10" t="n">
-        <v>58327</v>
+        <v>57525</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1674,16 +1674,16 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103044</v>
+        <v>100096</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Fiskgjuse</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Pandion haliaetus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">

--- a/artfynd/A 16982-2023 artfynd.xlsx
+++ b/artfynd/A 16982-2023 artfynd.xlsx
@@ -1417,10 +1417,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125893499</v>
+        <v>125893478</v>
       </c>
       <c r="B8" t="n">
-        <v>58327</v>
+        <v>57525</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1428,16 +1428,16 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103044</v>
+        <v>100096</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Fiskgjuse</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Pandion haliaetus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1540,44 +1540,44 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125893492</v>
+        <v>125893499</v>
       </c>
       <c r="B9" t="n">
-        <v>58080</v>
+        <v>58327</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103001</v>
+        <v>103044</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>förbiflygande</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
@@ -1663,44 +1663,44 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125893478</v>
+        <v>125893492</v>
       </c>
       <c r="B10" t="n">
-        <v>57525</v>
+        <v>58080</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100096</v>
+        <v>103001</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Fiskgjuse</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pandion haliaetus</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1766</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>förbiflygande</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>

--- a/artfynd/A 16982-2023 artfynd.xlsx
+++ b/artfynd/A 16982-2023 artfynd.xlsx
@@ -1540,44 +1540,44 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125893499</v>
+        <v>125893492</v>
       </c>
       <c r="B9" t="n">
-        <v>58327</v>
+        <v>58080</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103044</v>
+        <v>103001</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1766</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>förbiflygande</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
@@ -1663,44 +1663,44 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125893492</v>
+        <v>125893499</v>
       </c>
       <c r="B10" t="n">
-        <v>58080</v>
+        <v>58327</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103001</v>
+        <v>103044</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>förbiflygande</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>

--- a/artfynd/A 16982-2023 artfynd.xlsx
+++ b/artfynd/A 16982-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125893477</v>
       </c>
       <c r="B2" t="n">
-        <v>57258</v>
+        <v>57262</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -801,7 +801,7 @@
         <v>125893495</v>
       </c>
       <c r="B3" t="n">
-        <v>58155</v>
+        <v>58159</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -924,7 +924,7 @@
         <v>125893485</v>
       </c>
       <c r="B4" t="n">
-        <v>57602</v>
+        <v>57606</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1047,7 +1047,7 @@
         <v>125893474</v>
       </c>
       <c r="B5" t="n">
-        <v>56959</v>
+        <v>56963</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1170,7 +1170,7 @@
         <v>125893493</v>
       </c>
       <c r="B6" t="n">
-        <v>58085</v>
+        <v>58089</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1293,7 +1293,7 @@
         <v>125893484</v>
       </c>
       <c r="B7" t="n">
-        <v>57598</v>
+        <v>57602</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1420,7 +1420,7 @@
         <v>125893478</v>
       </c>
       <c r="B8" t="n">
-        <v>57525</v>
+        <v>57529</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1540,44 +1540,44 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125893492</v>
+        <v>125893499</v>
       </c>
       <c r="B9" t="n">
-        <v>58080</v>
+        <v>58331</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103001</v>
+        <v>103044</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>förbiflygande</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
@@ -1663,44 +1663,44 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125893499</v>
+        <v>125893492</v>
       </c>
       <c r="B10" t="n">
-        <v>58327</v>
+        <v>58084</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103044</v>
+        <v>103001</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1766</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>förbiflygande</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
@@ -1789,7 +1789,7 @@
         <v>125893472</v>
       </c>
       <c r="B11" t="n">
-        <v>57474</v>
+        <v>57478</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 16982-2023 artfynd.xlsx
+++ b/artfynd/A 16982-2023 artfynd.xlsx
@@ -1540,44 +1540,44 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125893499</v>
+        <v>125893492</v>
       </c>
       <c r="B9" t="n">
-        <v>58331</v>
+        <v>58084</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103044</v>
+        <v>103001</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1766</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>förbiflygande</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
@@ -1663,44 +1663,44 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125893492</v>
+        <v>125893499</v>
       </c>
       <c r="B10" t="n">
-        <v>58084</v>
+        <v>58331</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103001</v>
+        <v>103044</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>förbiflygande</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>

--- a/artfynd/A 16982-2023 artfynd.xlsx
+++ b/artfynd/A 16982-2023 artfynd.xlsx
@@ -1417,44 +1417,44 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125893478</v>
+        <v>125893492</v>
       </c>
       <c r="B8" t="n">
-        <v>57529</v>
+        <v>58084</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100096</v>
+        <v>103001</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Fiskgjuse</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pandion haliaetus</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1766</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>förbiflygande</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
@@ -1540,44 +1540,44 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125893492</v>
+        <v>125893499</v>
       </c>
       <c r="B9" t="n">
-        <v>58084</v>
+        <v>58331</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103001</v>
+        <v>103044</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>förbiflygande</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
@@ -1663,10 +1663,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125893499</v>
+        <v>125893478</v>
       </c>
       <c r="B10" t="n">
-        <v>58331</v>
+        <v>57529</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1674,16 +1674,16 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103044</v>
+        <v>100096</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Fiskgjuse</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Pandion haliaetus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">

--- a/artfynd/A 16982-2023 artfynd.xlsx
+++ b/artfynd/A 16982-2023 artfynd.xlsx
@@ -1540,10 +1540,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125893499</v>
+        <v>125893478</v>
       </c>
       <c r="B9" t="n">
-        <v>58331</v>
+        <v>57529</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1551,16 +1551,16 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103044</v>
+        <v>100096</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Fiskgjuse</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Pandion haliaetus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1663,10 +1663,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125893478</v>
+        <v>125893499</v>
       </c>
       <c r="B10" t="n">
-        <v>57529</v>
+        <v>58331</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1674,16 +1674,16 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100096</v>
+        <v>103044</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Fiskgjuse</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pandion haliaetus</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">

--- a/artfynd/A 16982-2023 artfynd.xlsx
+++ b/artfynd/A 16982-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125893477</v>
       </c>
       <c r="B2" t="n">
-        <v>57262</v>
+        <v>57263</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -801,7 +801,7 @@
         <v>125893495</v>
       </c>
       <c r="B3" t="n">
-        <v>58159</v>
+        <v>58162</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -924,7 +924,7 @@
         <v>125893485</v>
       </c>
       <c r="B4" t="n">
-        <v>57606</v>
+        <v>57607</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1047,7 +1047,7 @@
         <v>125893474</v>
       </c>
       <c r="B5" t="n">
-        <v>56963</v>
+        <v>56964</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1170,7 +1170,7 @@
         <v>125893493</v>
       </c>
       <c r="B6" t="n">
-        <v>58089</v>
+        <v>58092</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1293,7 +1293,7 @@
         <v>125893484</v>
       </c>
       <c r="B7" t="n">
-        <v>57602</v>
+        <v>57603</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1417,44 +1417,44 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125893492</v>
+        <v>125893478</v>
       </c>
       <c r="B8" t="n">
-        <v>58084</v>
+        <v>57530</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103001</v>
+        <v>100096</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Fiskgjuse</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Pandion haliaetus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>förbiflygande</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
@@ -1540,44 +1540,44 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125893478</v>
+        <v>125893492</v>
       </c>
       <c r="B9" t="n">
-        <v>57529</v>
+        <v>58087</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100096</v>
+        <v>103001</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Fiskgjuse</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pandion haliaetus</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1766</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>förbiflygande</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
@@ -1666,7 +1666,7 @@
         <v>125893499</v>
       </c>
       <c r="B10" t="n">
-        <v>58331</v>
+        <v>58334</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1789,7 +1789,7 @@
         <v>125893472</v>
       </c>
       <c r="B11" t="n">
-        <v>57478</v>
+        <v>57479</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 16982-2023 artfynd.xlsx
+++ b/artfynd/A 16982-2023 artfynd.xlsx
@@ -1417,10 +1417,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125893478</v>
+        <v>125893499</v>
       </c>
       <c r="B8" t="n">
-        <v>57530</v>
+        <v>58334</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1428,16 +1428,16 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100096</v>
+        <v>103044</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Fiskgjuse</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pandion haliaetus</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1540,44 +1540,44 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125893492</v>
+        <v>125893478</v>
       </c>
       <c r="B9" t="n">
-        <v>58087</v>
+        <v>57530</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103001</v>
+        <v>100096</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Fiskgjuse</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Pandion haliaetus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>förbiflygande</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
@@ -1663,44 +1663,44 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125893499</v>
+        <v>125893492</v>
       </c>
       <c r="B10" t="n">
-        <v>58334</v>
+        <v>58087</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103044</v>
+        <v>103001</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1766</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>förbiflygande</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>

--- a/artfynd/A 16982-2023 artfynd.xlsx
+++ b/artfynd/A 16982-2023 artfynd.xlsx
@@ -1417,10 +1417,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125893499</v>
+        <v>125893478</v>
       </c>
       <c r="B8" t="n">
-        <v>58334</v>
+        <v>57530</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1428,16 +1428,16 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103044</v>
+        <v>100096</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Fiskgjuse</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Pandion haliaetus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1540,44 +1540,44 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125893478</v>
+        <v>125893492</v>
       </c>
       <c r="B9" t="n">
-        <v>57530</v>
+        <v>58087</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100096</v>
+        <v>103001</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Fiskgjuse</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pandion haliaetus</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1766</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>förbiflygande</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
@@ -1663,44 +1663,44 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125893492</v>
+        <v>125893499</v>
       </c>
       <c r="B10" t="n">
-        <v>58087</v>
+        <v>58334</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103001</v>
+        <v>103044</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>förbiflygande</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>

--- a/artfynd/A 16982-2023 artfynd.xlsx
+++ b/artfynd/A 16982-2023 artfynd.xlsx
@@ -1540,44 +1540,44 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125893492</v>
+        <v>125893499</v>
       </c>
       <c r="B9" t="n">
-        <v>58087</v>
+        <v>58334</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103001</v>
+        <v>103044</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>förbiflygande</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
@@ -1663,44 +1663,44 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125893499</v>
+        <v>125893492</v>
       </c>
       <c r="B10" t="n">
-        <v>58334</v>
+        <v>58087</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103044</v>
+        <v>103001</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1766</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>förbiflygande</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
